--- a/Logistic.xlsx
+++ b/Logistic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1461,19 +1461,41 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>DE26011N</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E45" s="4">
+        <f>C45*D45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr"/>
-      <c r="C45" s="6">
-        <f>SUM(C2:C44)</f>
-        <v/>
-      </c>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="7">
-        <f>SUM(E2:E44)</f>
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="6">
+        <f>SUM(C2:C45)</f>
+        <v/>
+      </c>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="7">
+        <f>SUM(E2:E45)</f>
         <v/>
       </c>
     </row>
@@ -1488,12 +1510,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1686,22 +1708,42 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1110</v>
+      </c>
+      <c r="E10" s="4">
+        <f>IF(C10&gt;0, D10/C10, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="6">
-        <f>SUM(C2:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="7">
-        <f>SUM(D2:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="7">
-        <f>IF(C10&gt;0, D10/C10, 0)</f>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="6">
+        <f>SUM(C2:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="7">
+        <f>SUM(D2:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="7">
+        <f>IF(C11&gt;0, D11/C11, 0)</f>
         <v/>
       </c>
     </row>

--- a/Logistic.xlsx
+++ b/Logistic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1463,7 +1463,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1483,19 +1483,371 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>DE26011B</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E46" s="4">
+        <f>C46*D46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>DE26011G</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E47" s="4">
+        <f>C47*D47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>DE26011P</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E48" s="4">
+        <f>C48*D48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>DE26011R</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E49" s="4">
+        <f>C49*D49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>DE26010B</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E50" s="4">
+        <f>C50*D50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>DE26010G</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E51" s="4">
+        <f>C51*D51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>DE26010M</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E52" s="4">
+        <f>C52*D52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>DE26010N</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E53" s="4">
+        <f>C53*D53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>DE26010R</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E54" s="4">
+        <f>C54*D54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>DE26012K</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="E55" s="4">
+        <f>C55*D55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>DE26012B</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="E56" s="4">
+        <f>C56*D56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>DE26010B</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E57" s="4">
+        <f>C57*D57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>DE26010G</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E58" s="4">
+        <f>C58*D58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>DE26010M</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E59" s="4">
+        <f>C59*D59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>DE26010N</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E60" s="4">
+        <f>C60*D60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>DE26010R</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="E61" s="4">
+        <f>C61*D61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr"/>
-      <c r="C46" s="6">
-        <f>SUM(C2:C45)</f>
-        <v/>
-      </c>
-      <c r="D46" s="5" t="inlineStr"/>
-      <c r="E46" s="7">
-        <f>SUM(E2:E45)</f>
+      <c r="B62" s="5" t="inlineStr"/>
+      <c r="C62" s="6">
+        <f>SUM(C2:C61)</f>
+        <v/>
+      </c>
+      <c r="D62" s="5" t="inlineStr"/>
+      <c r="E62" s="7">
+        <f>SUM(E2:E61)</f>
         <v/>
       </c>
     </row>
@@ -1510,7 +1862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1710,17 +2062,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1110</v>
+        <v>10915</v>
       </c>
       <c r="E10" s="4">
         <f>IF(C10&gt;0, D10/C10, 0)</f>
@@ -1728,22 +2080,62 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>5400</v>
+      </c>
+      <c r="E11" s="4">
+        <f>IF(C11&gt;0, D11/C11, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>10730</v>
+      </c>
+      <c r="E12" s="4">
+        <f>IF(C12&gt;0, D12/C12, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Total Summary</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="6">
-        <f>SUM(C2:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="7">
-        <f>SUM(D2:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="7">
-        <f>IF(C11&gt;0, D11/C11, 0)</f>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="6">
+        <f>SUM(C2:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="7">
+        <f>SUM(D2:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="7">
+        <f>IF(C13&gt;0, D13/C13, 0)</f>
         <v/>
       </c>
     </row>
